--- a/artfynd/A 22648-2024 artfynd.xlsx
+++ b/artfynd/A 22648-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>117961878</v>
       </c>
       <c r="B2" t="n">
-        <v>57303</v>
+        <v>57304</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>117961957</v>
       </c>
       <c r="B3" t="n">
-        <v>97857</v>
+        <v>97859</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
